--- a/Weekly/Assignment2_Git/SauceDemo_Manual_Testing.xlsx
+++ b/Weekly/Assignment2_Git/SauceDemo_Manual_Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0GSI Master Class\GSI Assignments\Weekly\Assignment2_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8F4AE0E-FCE9-452B-A617-7BFCB3A757F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7273E65F-44A2-496A-A8A2-0878FD075FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="117">
   <si>
     <t>Website Under Test</t>
   </si>
@@ -76,15 +76,6 @@
     <t>Part 1: Functional Testing</t>
   </si>
   <si>
-    <t>TC ID</t>
-  </si>
-  <si>
-    <t>Test Scenario</t>
-  </si>
-  <si>
-    <t>Test Steps</t>
-  </si>
-  <si>
     <t>Expected Result</t>
   </si>
   <si>
@@ -100,12 +91,6 @@
     <t>Login with valid credentials</t>
   </si>
   <si>
-    <t>1. Go to https://www.saucedemo.com
-2. Enter Username: standard_user
-3. Enter Password: secret_sauce
-4. Click 'Login'</t>
-  </si>
-  <si>
     <t>User logged in successfully and redirected to the Products page</t>
   </si>
   <si>
@@ -121,12 +106,6 @@
     <t>Login with invalid password</t>
   </si>
   <si>
-    <t>1. Go to login page
-2. Enter Username: standard_user
-3. Enter an incorrect password (e.g. wrong_pass)
-4. Click 'Login'</t>
-  </si>
-  <si>
     <t>Error message displayed</t>
   </si>
   <si>
@@ -139,10 +118,6 @@
     <t>Add one product to cart</t>
   </si>
   <si>
-    <t>1. Login with valid credentials
-2. On Products page, click 'Add to cart' on any item (e.g. Sauce Labs Backpack)</t>
-  </si>
-  <si>
     <t>Product added to cart</t>
   </si>
   <si>
@@ -155,9 +130,6 @@
     <t>Remove product from cart</t>
   </si>
   <si>
-    <t>1. With one item already in the cart, click 'Remove' on that item (Products page or Cart page)</t>
-  </si>
-  <si>
     <t>Product removed from cart</t>
   </si>
   <si>
@@ -168,10 +140,6 @@
   </si>
   <si>
     <t>Sort products Low to High</t>
-  </si>
-  <si>
-    <t>1. On Products page, open the sort dropdown (default 'Name (A to Z)')
-2. Select 'Price (low to high)'</t>
   </si>
   <si>
     <t>Products sorted by price, ascending</t>
@@ -311,6 +279,122 @@
   </si>
   <si>
     <t>Anupam Mohanty</t>
+  </si>
+  <si>
+    <t>Test Case Id</t>
+  </si>
+  <si>
+    <t>Requirement Id</t>
+  </si>
+  <si>
+    <t>Test Case Scenario</t>
+  </si>
+  <si>
+    <t>Test Case Description</t>
+  </si>
+  <si>
+    <t>Precondition</t>
+  </si>
+  <si>
+    <t>Test Case Steps Taken</t>
+  </si>
+  <si>
+    <t>REQ_LOGIN_01</t>
+  </si>
+  <si>
+    <t>Verify that a registered user can log in successfully using valid credentials.</t>
+  </si>
+  <si>
+    <t>User has a registered SauceDemo account; browser is open at the login page.</t>
+  </si>
+  <si>
+    <t>1. Go to https://www.saucedemo.com
+2. Enter Username
+3. Enter Password
+4. Click 'Login'</t>
+  </si>
+  <si>
+    <t>REQ_LOGIN_02</t>
+  </si>
+  <si>
+    <t>Verify that the system rejects login and shows an error when the password is incorrect.</t>
+  </si>
+  <si>
+    <t>1. Go to login page
+2. Enter Username
+3. Enter an incorrect Password
+4. Click 'Login'</t>
+  </si>
+  <si>
+    <t>REQ_CART_01</t>
+  </si>
+  <si>
+    <t>Verify that a user can add a single product to the cart from the Products page.</t>
+  </si>
+  <si>
+    <t>User is logged in and on the Products page.</t>
+  </si>
+  <si>
+    <t>1. On Products page, locate a product
+2. Click 'Add to cart' on that item</t>
+  </si>
+  <si>
+    <t>REQ_CART_02</t>
+  </si>
+  <si>
+    <t>Verify that a user can remove a previously added product from the cart.</t>
+  </si>
+  <si>
+    <t>User is logged in and has at least one item already in the cart.</t>
+  </si>
+  <si>
+    <t>1. Locate the item already in cart (Products or Cart page)
+2. Click 'Remove' on that item</t>
+  </si>
+  <si>
+    <t>REQ_SORT_01</t>
+  </si>
+  <si>
+    <t>Verify that the product sort dropdown correctly orders items by ascending price.</t>
+  </si>
+  <si>
+    <t>1. Open the sort dropdown (default 'Name (A to Z)')
+2. Select 'Price (low to high)'</t>
+  </si>
+  <si>
+    <t>REQ_LOGOUT_01</t>
+  </si>
+  <si>
+    <t>Verify that a logged-in user can log out and is returned to the login page.</t>
+  </si>
+  <si>
+    <t>User is logged in to the application.</t>
+  </si>
+  <si>
+    <t>Test Data</t>
+  </si>
+  <si>
+    <t>Defect Id</t>
+  </si>
+  <si>
+    <t>Username: standard_user
+Password: secret_sauce</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Username: standard_user
+Password: wrong_pass</t>
+  </si>
+  <si>
+    <t>Product: Sauce Labs Backpack</t>
+  </si>
+  <si>
+    <t>Product: Sauce Labs Backpack (already in cart)</t>
+  </si>
+  <si>
+    <t>Sort option: Price (low to high)</t>
   </si>
 </sst>
 </file>
@@ -432,24 +516,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -474,6 +542,25 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -750,161 +837,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
+      <c r="A1" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="6"/>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="C6" s="10"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10"/>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" spans="1:6" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="10"/>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="5"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10"/>
+      <c r="F9" s="10"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5"/>
+      <c r="B10" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="C10" s="10"/>
+      <c r="D10" s="10"/>
+      <c r="E10" s="10"/>
+      <c r="F10" s="10"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="11"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
+      <c r="A13" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="B4:F4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B7:F7"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B10:F10"/>
     <mergeCell ref="A12:F12"/>
     <mergeCell ref="A13:F16"/>
-    <mergeCell ref="A1:F2"/>
-    <mergeCell ref="B4:F4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B7:F7"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -916,7 +1003,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -924,162 +1011,275 @@
     <col min="3" max="3" width="42" customWidth="1"/>
     <col min="4" max="4" width="32" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="31.5546875" customWidth="1"/>
+    <col min="7" max="7" width="42.5546875" customWidth="1"/>
+    <col min="8" max="9" width="36.5546875" customWidth="1"/>
+    <col min="10" max="10" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="16"/>
+      <c r="K1" s="16"/>
+    </row>
+    <row r="2" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="K2" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="B3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="D3" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="H3" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="I3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="J3" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="9" t="s">
+      <c r="K3" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="B4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="D4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="I4" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
+      <c r="J4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="D5" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="I5" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="J5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
+      <c r="B6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="D6" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="H6" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="I6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="J6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E5" s="9" t="s">
+      <c r="B7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F5" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
+      <c r="D7" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B6" s="11" t="s">
+      <c r="I7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="J7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="11" t="s">
+      <c r="B8" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E6" s="11" t="s">
+      <c r="D8" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
+      <c r="G8" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="H8" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="I8" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="E7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="F7" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>25</v>
+      <c r="J8" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="K8" s="5" t="s">
+        <v>112</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -1100,65 +1300,65 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>1</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="8">
+        <v>2</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>3</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="8">
+        <v>4</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="C6" s="5" t="s">
         <v>52</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="14">
-        <v>2</v>
-      </c>
-      <c r="B4" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <v>3</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="14">
-        <v>4</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1184,70 +1384,70 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" s="8" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="48" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3"/>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
+      <c r="A8" s="12"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="12"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="3"/>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
+      <c r="A9" s="12"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1273,87 +1473,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="B5" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B2" s="8" t="s">
+    </row>
+    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="B6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="11" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C5" s="9" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="9" t="s">
-        <v>84</v>
-      </c>
-    </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="1"/>
+      <c r="A9" s="15"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="15"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/Weekly/Assignment2_Git/SauceDemo_Manual_Testing.xlsx
+++ b/Weekly/Assignment2_Git/SauceDemo_Manual_Testing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\0GSI Master Class\GSI Assignments\Weekly\Assignment2_Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7273E65F-44A2-496A-A8A2-0878FD075FBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CB07A04-8228-413E-B48D-953E4E8861CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -224,9 +224,6 @@
     <t>None observed. The app uses standard, widely-supported web APIs with no Chromium-specific dependencies, so no Firefox rendering issues are expected.</t>
   </si>
   <si>
-    <t>Part 3: Smoke Testing (Post-Deployment)</t>
-  </si>
-  <si>
     <t>Check</t>
   </si>
   <si>
@@ -395,6 +392,9 @@
   </si>
   <si>
     <t>Sort option: Price (low to high)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part 3: Smoke Testing </t>
   </si>
 </sst>
 </file>
@@ -543,6 +543,9 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -550,7 +553,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -558,9 +561,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -837,161 +837,161 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
+      <c r="A1" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="10"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="11"/>
     </row>
     <row r="6" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
     </row>
     <row r="7" spans="1:6" ht="23.85" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="10"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
     </row>
     <row r="8" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10" t="s">
+      <c r="B8" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="10"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="11"/>
     </row>
     <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="10"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="11"/>
     </row>
     <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
-      <c r="E10" s="10"/>
-      <c r="F10" s="10"/>
+      <c r="B10" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
     </row>
     <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="B13" s="12"/>
-      <c r="C13" s="12"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="F13" s="12"/>
+      <c r="A13" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" s="13"/>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="12"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="12"/>
+      <c r="A14" s="13"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="13"/>
+      <c r="F14" s="13"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="12"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="12"/>
-      <c r="D15" s="12"/>
-      <c r="E15" s="12"/>
-      <c r="F15" s="12"/>
+      <c r="A15" s="13"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="12"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="12"/>
-      <c r="D16" s="12"/>
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
+      <c r="A16" s="13"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+      <c r="F16" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B10:F10"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:F16"/>
     <mergeCell ref="A1:F2"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B10:F10"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:F16"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
@@ -1018,41 +1018,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-    </row>
-    <row r="2" spans="1:11" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+      <c r="J1" s="14"/>
+      <c r="K1" s="14"/>
+    </row>
+    <row r="2" spans="1:11" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>14</v>
@@ -1064,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1072,22 +1072,22 @@
         <v>17</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>91</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>19</v>
@@ -1099,7 +1099,7 @@
         <v>21</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1107,22 +1107,22 @@
         <v>22</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>23</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>94</v>
-      </c>
       <c r="G4" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>24</v>
@@ -1134,7 +1134,7 @@
         <v>21</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1142,22 +1142,22 @@
         <v>26</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="G5" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>28</v>
@@ -1169,7 +1169,7 @@
         <v>21</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1177,22 +1177,22 @@
         <v>30</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>31</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="F6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>102</v>
-      </c>
       <c r="G6" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>32</v>
@@ -1204,7 +1204,7 @@
         <v>21</v>
       </c>
       <c r="K6" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1212,22 +1212,22 @@
         <v>34</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C7" s="3" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="G7" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>36</v>
@@ -1239,7 +1239,7 @@
         <v>21</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1247,22 +1247,22 @@
         <v>38</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>39</v>
       </c>
       <c r="D8" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>107</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>108</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>40</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>41</v>
@@ -1274,7 +1274,7 @@
         <v>21</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -1300,11 +1300,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1325,7 +1325,7 @@
         <v>47</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1336,7 +1336,7 @@
         <v>48</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="69.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -1384,11 +1384,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
@@ -1435,19 +1435,19 @@
       </c>
     </row>
     <row r="7" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
+      <c r="A7" s="13"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A8" s="12"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
+      <c r="A8" s="13"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A9" s="12"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="12"/>
+      <c r="A9" s="13"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1473,87 +1473,87 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
+      <c r="A1" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>21</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15"/>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
+      <c r="A9" s="16"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="A10" s="16"/>
+      <c r="B10" s="16"/>
+      <c r="C10" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="2">
